--- a/個別支援計画案.xlsx
+++ b/個別支援計画案.xlsx
@@ -30,16 +30,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
-    <t>個別支援計画</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">コベツ </t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t xml:space="preserve">シエンケイカク </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>利用者氏名：</t>
     <rPh sb="0" eb="3">
       <t xml:space="preserve">リヨウシャ </t>
@@ -254,6 +244,19 @@
     </rPh>
     <rPh sb="34" eb="35">
       <t xml:space="preserve">イン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>個別支援計画(案)</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">コベツ </t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t xml:space="preserve">シエンケイカク </t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -985,7 +988,7 @@
     <row r="1" spans="2:18" ht="5.4" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:18" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="49" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
@@ -1044,7 +1047,7 @@
     </row>
     <row r="5" spans="2:18" ht="19.8" x14ac:dyDescent="0.2">
       <c r="B5" s="50" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="50"/>
@@ -1053,28 +1056,28 @@
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
       <c r="I5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10" t="s">
         <v>2</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>3</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
@@ -1114,7 +1117,7 @@
     </row>
     <row r="9" spans="2:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26"/>
@@ -1154,7 +1157,7 @@
     </row>
     <row r="11" spans="2:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26"/>
@@ -1196,31 +1199,31 @@
     <row r="14" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="28"/>
       <c r="C14" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="32"/>
       <c r="G14" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H14" s="31"/>
       <c r="I14" s="32"/>
       <c r="J14" s="39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K14" s="40"/>
       <c r="L14" s="40"/>
       <c r="M14" s="39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N14" s="40"/>
       <c r="O14" s="30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P14" s="32"/>
       <c r="Q14" s="43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R14" s="44"/>
     </row>
@@ -1327,7 +1330,7 @@
     </row>
     <row r="20" spans="2:18" ht="22.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -1340,23 +1343,23 @@
     <row r="21" spans="2:18" ht="26.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="7"/>
       <c r="D21" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" s="9"/>
       <c r="H21" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
       <c r="L21" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="14"/>
